--- a/2025/meet_list.xlsx
+++ b/2025/meet_list.xlsx
@@ -2953,7 +2953,7 @@
         <v>1</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79" s="7">
         <v>0</v>
